--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2702_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2702_SW2.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>Air-Way FF2702 (s29, double-pass 2026-10-15, parts.air-way.com/api/series/29, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2702-08-08-FG (ORFS-p008-t04); FORGED part: Air-Way NON-forged row FF2702-8-8-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length = gen_straight2 FSM_MEAS (Brennan FS2403-08-08); on the forged legs the thread major runs to the end length and steps down to the hex flats (Brennan FS6500 / FS6801 / FS2701-08 forged legs) - the end stands proud of the flats; hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); face-seal bulkhead leg (Brennan FS2701-08-08-FG): FSM nose, face-seal thread to a 60deg flank and a relief, then a step of Air-Way i4 (i4 = the length of that step on the STEP, not the collar thickness), the collar face at Air-Way i2 from the tip, collar dia = Air-Way d17 (column D17@BORE, a collar dia), collar thickness and step dia / relief length measured on the -08 pilot (FSBH_MEAS; Air-Way prints no collar thickness - other sizes need their own STEP); -LN rows = the plain part, the locknut is a separate part (user A10); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF2702 (s29, double-pass 2026-10-15, parts.air-way.com/api/series/29, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2702-08-08-FG (ORFS-p008-t04); FORGED part: Air-Way NON-forged row FF2702-8-8-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); face-seal bulkhead leg (Brennan FS2701-08-08-FG): FSM nose, face-seal thread to a 60deg flank and a relief, then a step of Air-Way i4 (i4 = the length of that step on the STEP, not the collar thickness), the collar face at Air-Way i2 from the tip, collar dia = Air-Way d17 (column D17@BORE, a collar dia), collar thickness and step dia / relief length measured on the -08 pilot (FSBH_MEAS; Air-Way prints no collar thickness - other sizes need their own STEP); -LN rows = the plain part, the locknut is a separate part (user A10); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>Air-Way FF2702 (s29, double-pass 2026-10-15, parts.air-way.com/api/series/29, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2702-08-08-FG (ORFS-p008-t04); FORGED part: Air-Way NON-forged row FF2702-8-8-LN-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length = gen_straight2 FSM_MEAS (Brennan FS2403-08-08); on the forged legs the thread major runs to the end length and steps down to the hex flats (Brennan FS6500 / FS6801 / FS2701-08 forged legs) - the end stands proud of the flats; hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); face-seal bulkhead leg (Brennan FS2701-08-08-FG): FSM nose, face-seal thread to a 60deg flank and a relief, then a step of Air-Way i4 (i4 = the length of that step on the STEP, not the collar thickness), the collar face at Air-Way i2 from the tip, collar dia = Air-Way d17 (column D17@BORE, a collar dia), collar thickness and step dia / relief length measured on the -08 pilot (FSBH_MEAS; Air-Way prints no collar thickness - other sizes need their own STEP); -LN rows = the plain part, the locknut is a separate part (user A10); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF2702 (s29, double-pass 2026-10-15, parts.air-way.com/api/series/29, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2702-08-08-FG (ORFS-p008-t04); FORGED part: Air-Way NON-forged row FF2702-8-8-LN-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); face-seal bulkhead leg (Brennan FS2701-08-08-FG): FSM nose, face-seal thread to a 60deg flank and a relief, then a step of Air-Way i4 (i4 = the length of that step on the STEP, not the collar thickness), the collar face at Air-Way i2 from the tip, collar dia = Air-Way d17 (column D17@BORE, a collar dia), collar thickness and step dia / relief length measured on the -08 pilot (FSBH_MEAS; Air-Way prints no collar thickness - other sizes need their own STEP); -LN rows = the plain part, the locknut is a separate part (user A10); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">

--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2702_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2702_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
